--- a/www/Bioerosion_Data_TEMPLATE.xlsx
+++ b/www/Bioerosion_Data_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC6B574-F0B7-4002-9D9D-28970EAA1166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AABF2D7-09F7-438F-A591-0B75CF08A0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="22020" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{19050643-5FB9-4299-B24C-C8F9EBB4329D}"/>
+    <workbookView xWindow="0" yWindow="735" windowWidth="28905" windowHeight="11190" xr2:uid="{19050643-5FB9-4299-B24C-C8F9EBB4329D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t xml:space="preserve">•  Sponges abundance should be quantified as total area in centimeters squared (cm2) occupied by each species; if survey data is instead in percent cover, it should be converted to area by multiplying the percent cover by Survey_Area_Sponges_m2 and then multiplying by 10,000 to covert m2 to cm2 </t>
   </si>
   <si>
-    <t xml:space="preserve">• Provide the area (in meters squared [m2]) where urchin surveys were conducted in Survey_Area_Sponges_m2; For example a 1 x 10 m belt transect would have a 10 m2 survey area </t>
-  </si>
-  <si>
     <t>Survey_Area_Sponges_m2</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>•  Input the monitoring timepoint in Years_Post_Restoration; months should be entered as fractional years, e.g., 3 months post outplanting = 0.25 y; pre-retoration data should be entered as -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Provide the area (in meters squared [m2]) where sponge surveys were conducted in Survey_Area_Sponges_m2; For example a 1 x 10 m belt transect would have a 10 m2 survey area </t>
   </si>
 </sst>
 </file>
@@ -613,7 +613,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
@@ -688,7 +688,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +729,7 @@
         <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -778,7 +778,7 @@
         <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -816,10 +816,10 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -833,26 +833,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -1047,26 +1027,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB6342C-EC7C-49F8-97E7-6339AB75B937}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC9D92C-6A9E-424D-BBA1-C74B9FBA6A28}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1085,6 +1066,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB6342C-EC7C-49F8-97E7-6339AB75B937}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
